--- a/output/RKM_Ступень_фигурная_5150x410x150.xlsx
+++ b/output/RKM_Ступень_фигурная_5150x410x150.xlsx
@@ -2069,7 +2069,7 @@
         <v>49</v>
       </c>
       <c r="E9" s="5">
-        <v>160000</v>
+        <v>170200</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2505,7 +2505,7 @@
         <v>120</v>
       </c>
       <c r="F10" s="13">
-        <v>114933.16799999999</v>
+        <v>122260.15745999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2522,7 +2522,7 @@
         <v>123</v>
       </c>
       <c r="F11" s="13">
-        <v>114933.16799999999</v>
+        <v>122260.15745999999</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2723,7 +2723,7 @@
         <v>0.7183322999999999</v>
       </c>
       <c r="E5" s="18">
-        <v>160000</v>
+        <v>170200</v>
       </c>
       <c r="F5" s="13">
         <f>D5*E5</f>
@@ -5039,7 +5039,7 @@
         <v>327</v>
       </c>
       <c r="B5" s="13">
-        <v>204033.168</v>
+        <v>211360.15746</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>328</v>
@@ -5083,7 +5083,7 @@
         <v>335</v>
       </c>
       <c r="B9" s="13">
-        <v>354515.32712984</v>
+        <v>361842.31658984</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>336</v>
@@ -5094,7 +5094,7 @@
         <v>337</v>
       </c>
       <c r="B10" s="13">
-        <v>28361.2261703872</v>
+        <v>28947.3853271872</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>338</v>
@@ -5105,7 +5105,7 @@
         <v>339</v>
       </c>
       <c r="B11" s="13">
-        <v>382876.55330022715</v>
+        <v>390789.7019170272</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>31</v>
@@ -5116,7 +5116,7 @@
         <v>340</v>
       </c>
       <c r="B12" s="13">
-        <v>130178.02812207724</v>
+        <v>132868.49865178924</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>341</v>
@@ -5127,7 +5127,7 @@
         <v>342</v>
       </c>
       <c r="B13" s="20">
-        <v>513054.5814223044</v>
+        <v>523658.2005688164</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>343</v>
@@ -5275,7 +5275,7 @@
         <v>363</v>
       </c>
       <c r="B15" s="13">
-        <v>2565.272907111522</v>
+        <v>2618.291002844082</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>364</v>
@@ -5335,7 +5335,7 @@
         <v>370</v>
       </c>
       <c r="B5" s="13">
-        <v>204033.168</v>
+        <v>211360.15746</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>31</v>
@@ -5368,7 +5368,7 @@
         <v>373</v>
       </c>
       <c r="B8" s="13">
-        <v>28361.2261703872</v>
+        <v>28947.3853271872</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>31</v>
@@ -5379,7 +5379,7 @@
         <v>374</v>
       </c>
       <c r="B9" s="13">
-        <v>130178.02812207724</v>
+        <v>132868.49865178924</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>31</v>
@@ -5390,7 +5390,7 @@
         <v>375</v>
       </c>
       <c r="B10" s="13">
-        <v>513054.5814223044</v>
+        <v>523658.2005688164</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>31</v>
@@ -5401,7 +5401,7 @@
         <v>376</v>
       </c>
       <c r="B11" s="13">
-        <v>175365.27290711153</v>
+        <v>175418.29100284408</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>31</v>
@@ -5412,7 +5412,7 @@
         <v>377</v>
       </c>
       <c r="B12" s="13">
-        <v>688419.854329416</v>
+        <v>699076.4915716605</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>31</v>
@@ -5423,7 +5423,7 @@
         <v>378</v>
       </c>
       <c r="B13" s="20">
-        <v>137683.9708658832</v>
+        <v>139815.29831433212</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>31</v>
@@ -5434,7 +5434,7 @@
         <v>379</v>
       </c>
       <c r="B14" s="26">
-        <v>826103.8251952991</v>
+        <v>838891.7898859926</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>31</v>
@@ -5445,7 +5445,7 @@
         <v>380</v>
       </c>
       <c r="B15" s="13">
-        <v>688419.854329416</v>
+        <v>699076.4915716605</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>31</v>
@@ -5456,7 +5456,7 @@
         <v>381</v>
       </c>
       <c r="B16" s="13">
-        <v>826103.8251952991</v>
+        <v>838891.7898859926</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>31</v>
@@ -5467,7 +5467,7 @@
         <v>382</v>
       </c>
       <c r="B17" s="20">
-        <v>326033.5563956505</v>
+        <v>331080.50749309047</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>383</v>
@@ -5478,7 +5478,7 @@
         <v>384</v>
       </c>
       <c r="B18" s="20">
-        <v>391240.26767478057</v>
+        <v>397296.6089917086</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>383</v>
@@ -5489,7 +5489,7 @@
         <v>385</v>
       </c>
       <c r="B19" s="13">
-        <v>133673.75812221668</v>
+        <v>135743.00807216708</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>386</v>
@@ -5500,7 +5500,7 @@
         <v>387</v>
       </c>
       <c r="B20" s="13">
-        <v>160408.50974666</v>
+        <v>162891.6096866005</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>386</v>
